--- a/web/public/forms/geomcheuk-yocheong.xlsx
+++ b/web/public/forms/geomcheuk-yocheong.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검측요청서 · 검측결과통보" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'검측요청서 · 검측결과통보'!$A$1:$X$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,8 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy&quot;년&quot; m&quot;월&quot; d&quot;일&quot;"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,29 +36,45 @@
       <name val="맑은 고딕"/>
       <b val="1"/>
       <color rgb="000F203F"/>
-      <sz val="10.5"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="006B7280"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="00111827"/>
       <sz val="19"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
       <b val="1"/>
-      <color rgb="000F203F"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="00222222"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F2937"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
@@ -65,7 +86,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F8FC"/>
+        <fgColor rgb="00F3F5F9"/>
       </patternFill>
     </fill>
   </fills>
@@ -79,23 +100,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </left>
       <right style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </right>
       <top style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFC7D5"/>
+        <color rgb="005B6573"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -104,26 +125,41 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -519,15 +555,15 @@
     <col width="3.6" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
+    <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵   |   k-conmap.com   무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다   </t>
+          <t xml:space="preserve">← 이 1행을 지우고 쓰셔도 됩니다  </t>
         </is>
       </c>
     </row>
@@ -551,7 +587,7 @@
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="5" t="n"/>
       <c r="I5" s="5" t="n"/>
       <c r="J5" s="5" t="n"/>
@@ -581,7 +617,7 @@
       <c r="D6" s="5" t="n"/>
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="n"/>
-      <c r="G6" s="6" t="inlineStr"/>
+      <c r="G6" s="7" t="n"/>
       <c r="H6" s="5" t="n"/>
       <c r="I6" s="5" t="n"/>
       <c r="J6" s="5" t="n"/>
@@ -645,7 +681,7 @@
       <c r="D8" s="5" t="n"/>
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="n"/>
       <c r="H8" s="5" t="n"/>
       <c r="I8" s="5" t="n"/>
       <c r="J8" s="5" t="n"/>
@@ -675,7 +711,7 @@
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="n"/>
       <c r="H9" s="5" t="n"/>
       <c r="I9" s="5" t="n"/>
       <c r="J9" s="5" t="n"/>
@@ -705,7 +741,7 @@
       <c r="D10" s="5" t="n"/>
       <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="n"/>
       <c r="H10" s="5" t="n"/>
       <c r="I10" s="5" t="n"/>
       <c r="J10" s="5" t="n"/>
@@ -735,7 +771,7 @@
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="n"/>
       <c r="H11" s="5" t="n"/>
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
@@ -756,15 +792,15 @@
     </row>
     <row r="12" ht="6" customHeight="1"/>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>위와 같이 세부공종에 대하여 검측을 요청하오니 검사 후 승인하여 주시기 바랍니다.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="6" customHeight="1"/>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>첨부 : 시공점검표(체크리스트) 점검결과 · 시험성과 · 야장 및 도면 · 공사참여자(기능공 포함) 명단 · 측량결과</t>
         </is>
@@ -773,19 +809,21 @@
     <row r="16" ht="6" customHeight="1"/>
     <row r="17" ht="10" customHeight="1"/>
     <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>년        월        일</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="K19" s="9" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          년        월        일</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="10" t="inlineStr"/>
+      <c r="K19" s="11" t="inlineStr">
         <is>
           <t>현장대리인</t>
         </is>
       </c>
-      <c r="S19" s="8" t="inlineStr">
+      <c r="Q19" s="12" t="n"/>
+      <c r="U19" s="13" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
@@ -793,7 +831,7 @@
     </row>
     <row r="20" ht="6" customHeight="1"/>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>────────────  검 측 결 과 통 보  ────────────</t>
         </is>
@@ -811,7 +849,7 @@
       <c r="D23" s="5" t="n"/>
       <c r="E23" s="5" t="n"/>
       <c r="F23" s="5" t="n"/>
-      <c r="G23" s="6" t="inlineStr"/>
+      <c r="G23" s="6" t="n"/>
       <c r="H23" s="5" t="n"/>
       <c r="I23" s="5" t="n"/>
       <c r="J23" s="5" t="n"/>
@@ -875,7 +913,7 @@
       <c r="D25" s="5" t="n"/>
       <c r="E25" s="5" t="n"/>
       <c r="F25" s="5" t="n"/>
-      <c r="G25" s="6" t="inlineStr"/>
+      <c r="G25" s="6" t="n"/>
       <c r="H25" s="5" t="n"/>
       <c r="I25" s="5" t="n"/>
       <c r="J25" s="5" t="n"/>
@@ -939,7 +977,7 @@
       <c r="D27" s="5" t="n"/>
       <c r="E27" s="5" t="n"/>
       <c r="F27" s="5" t="n"/>
-      <c r="G27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="n"/>
       <c r="H27" s="5" t="n"/>
       <c r="I27" s="5" t="n"/>
       <c r="J27" s="5" t="n"/>
@@ -959,8 +997,8 @@
       <c r="X27" s="5" t="n"/>
     </row>
     <row r="28" ht="6" customHeight="1"/>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>위 검측요청서 번호에 대한 검측결과를 다음과 같이 통보합니다.  붙임 : 감리원의 검측 체크리스트</t>
         </is>
@@ -969,47 +1007,57 @@
     <row r="30" ht="6" customHeight="1"/>
     <row r="31" ht="10" customHeight="1"/>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>년        월        일</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="K33" s="9" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          년        월        일</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="10" t="inlineStr"/>
+      <c r="K33" s="11" t="inlineStr">
         <is>
           <t>검측 감리원</t>
         </is>
       </c>
-      <c r="S33" s="8" t="inlineStr">
+      <c r="Q33" s="12" t="n"/>
+      <c r="U33" s="13" t="inlineStr">
         <is>
           <t>(서명 또는 인)</t>
         </is>
       </c>
     </row>
     <row r="34" ht="6" customHeight="1"/>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>발주기관이 정한 서식이 있으면 그 서식을 사용하세요. 이 줄과 1행은 인쇄 전에 지우셔도 됩니다.</t>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>노란 칸 = 요율·기준값(발주기관 기준으로 고쳐 씀) · 옅은 하늘색 칸 = 자동 계산(지우지 마세요) · 뒤 시트에 «작성 예시» 가 있습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="19.5" customHeight="1">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t>발주기관이 정한 서식이 있으면 그 서식을 쓰세요. 이 줄과 1행은 지워도 됩니다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="38">
+  <mergeCells count="43">
+    <mergeCell ref="U33:X33"/>
     <mergeCell ref="G7:X7"/>
     <mergeCell ref="A27:F27"/>
-    <mergeCell ref="K33:R33"/>
     <mergeCell ref="G10:X10"/>
+    <mergeCell ref="A33:J33"/>
     <mergeCell ref="G6:X6"/>
     <mergeCell ref="A37:X37"/>
     <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A19:J19"/>
     <mergeCell ref="A18:X18"/>
-    <mergeCell ref="S19:X19"/>
     <mergeCell ref="A3:X3"/>
+    <mergeCell ref="U19:X19"/>
     <mergeCell ref="A21:X21"/>
     <mergeCell ref="G24:X24"/>
-    <mergeCell ref="S33:X33"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="G5:X5"/>
@@ -1017,26 +1065,636 @@
     <mergeCell ref="A25:F25"/>
     <mergeCell ref="A32:X32"/>
     <mergeCell ref="G26:X26"/>
+    <mergeCell ref="Q33:T33"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A29:X29"/>
+    <mergeCell ref="K19:P19"/>
     <mergeCell ref="G25:X25"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="G9:X9"/>
     <mergeCell ref="A13:X13"/>
     <mergeCell ref="A24:F24"/>
+    <mergeCell ref="Q19:T19"/>
     <mergeCell ref="A11:F11"/>
+    <mergeCell ref="K33:P33"/>
     <mergeCell ref="G11:X11"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A15:X15"/>
     <mergeCell ref="G27:X27"/>
     <mergeCell ref="A6:F6"/>
-    <mergeCell ref="K19:R19"/>
     <mergeCell ref="M1:X1"/>
+    <mergeCell ref="A36:X36"/>
     <mergeCell ref="G23:X23"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="G8:X8"/>
   </mergeCells>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00F59E0B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:X36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3.6" customWidth="1" min="1" max="1"/>
+    <col width="3.6" customWidth="1" min="2" max="2"/>
+    <col width="3.6" customWidth="1" min="3" max="3"/>
+    <col width="3.6" customWidth="1" min="4" max="4"/>
+    <col width="3.6" customWidth="1" min="5" max="5"/>
+    <col width="3.6" customWidth="1" min="6" max="6"/>
+    <col width="3.6" customWidth="1" min="7" max="7"/>
+    <col width="3.6" customWidth="1" min="8" max="8"/>
+    <col width="3.6" customWidth="1" min="9" max="9"/>
+    <col width="3.6" customWidth="1" min="10" max="10"/>
+    <col width="3.6" customWidth="1" min="11" max="11"/>
+    <col width="3.6" customWidth="1" min="12" max="12"/>
+    <col width="3.6" customWidth="1" min="13" max="13"/>
+    <col width="3.6" customWidth="1" min="14" max="14"/>
+    <col width="3.6" customWidth="1" min="15" max="15"/>
+    <col width="3.6" customWidth="1" min="16" max="16"/>
+    <col width="3.6" customWidth="1" min="17" max="17"/>
+    <col width="3.6" customWidth="1" min="18" max="18"/>
+    <col width="3.6" customWidth="1" min="19" max="19"/>
+    <col width="3.6" customWidth="1" min="20" max="20"/>
+    <col width="3.6" customWidth="1" min="21" max="21"/>
+    <col width="3.6" customWidth="1" min="22" max="22"/>
+    <col width="3.6" customWidth="1" min="23" max="23"/>
+    <col width="3.6" customWidth="1" min="24" max="24"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="20" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+        </is>
+      </c>
+      <c r="M1" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="6" customHeight="1"/>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>검 측 요 청 서</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="10" customHeight="1"/>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  번        호</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>검측 제2026-041호</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="5" t="n"/>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
+      <c r="Q5" s="5" t="n"/>
+      <c r="R5" s="5" t="n"/>
+      <c r="S5" s="5" t="n"/>
+      <c r="T5" s="5" t="n"/>
+      <c r="U5" s="5" t="n"/>
+      <c r="V5" s="5" t="n"/>
+      <c r="W5" s="5" t="n"/>
+      <c r="X5" s="5" t="n"/>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  요 청 일 자</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="7" t="n">
+        <v>46293</v>
+      </c>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
+      <c r="Q6" s="5" t="n"/>
+      <c r="R6" s="5" t="n"/>
+      <c r="S6" s="5" t="n"/>
+      <c r="T6" s="5" t="n"/>
+      <c r="U6" s="5" t="n"/>
+      <c r="V6" s="5" t="n"/>
+      <c r="W6" s="5" t="n"/>
+      <c r="X6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  수        신</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>책임감리원 귀하</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="n"/>
+      <c r="I7" s="5" t="n"/>
+      <c r="J7" s="5" t="n"/>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
+      <c r="Q7" s="5" t="n"/>
+      <c r="R7" s="5" t="n"/>
+      <c r="S7" s="5" t="n"/>
+      <c r="T7" s="5" t="n"/>
+      <c r="U7" s="5" t="n"/>
+      <c r="V7" s="5" t="n"/>
+      <c r="W7" s="5" t="n"/>
+      <c r="X7" s="5" t="n"/>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  위치 및 공종</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>STA.0+420 ~ 0+462 · 배수공(PE관 D600)</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
+      <c r="I8" s="5" t="n"/>
+      <c r="J8" s="5" t="n"/>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
+      <c r="Q8" s="5" t="n"/>
+      <c r="R8" s="5" t="n"/>
+      <c r="S8" s="5" t="n"/>
+      <c r="T8" s="5" t="n"/>
+      <c r="U8" s="5" t="n"/>
+      <c r="V8" s="5" t="n"/>
+      <c r="W8" s="5" t="n"/>
+      <c r="X8" s="5" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  검 측 부 위</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n"/>
+      <c r="C9" s="5" t="n"/>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>관 기초·부설·접합부</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="5" t="n"/>
+      <c r="J9" s="5" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
+      <c r="Q9" s="5" t="n"/>
+      <c r="R9" s="5" t="n"/>
+      <c r="S9" s="5" t="n"/>
+      <c r="T9" s="5" t="n"/>
+      <c r="U9" s="5" t="n"/>
+      <c r="V9" s="5" t="n"/>
+      <c r="W9" s="5" t="n"/>
+      <c r="X9" s="5" t="n"/>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  검측 요구일시</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="5" t="n"/>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>2026. 9. 29. 10:00</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n"/>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="5" t="n"/>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
+      <c r="Q10" s="5" t="n"/>
+      <c r="R10" s="5" t="n"/>
+      <c r="S10" s="5" t="n"/>
+      <c r="T10" s="5" t="n"/>
+      <c r="U10" s="5" t="n"/>
+      <c r="V10" s="5" t="n"/>
+      <c r="W10" s="5" t="n"/>
+      <c r="X10" s="5" t="n"/>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  검 측 사 항</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>관 기초 모래 두께 · 관 구배 · 접합 수밀</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="5" t="n"/>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
+      <c r="Q11" s="5" t="n"/>
+      <c r="R11" s="5" t="n"/>
+      <c r="S11" s="5" t="n"/>
+      <c r="T11" s="5" t="n"/>
+      <c r="U11" s="5" t="n"/>
+      <c r="V11" s="5" t="n"/>
+      <c r="W11" s="5" t="n"/>
+      <c r="X11" s="5" t="n"/>
+    </row>
+    <row r="12" ht="6" customHeight="1"/>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>위와 같이 세부공종에 대하여 검측을 요청하오니 검사 후 승인하여 주시기 바랍니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="6" customHeight="1"/>
+    <row r="15" ht="34" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>첨부 : 시공점검표(체크리스트) 점검결과 · 시험성과 · 야장 및 도면 · 공사참여자(기능공 포함) 명단 · 측량결과</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="6" customHeight="1"/>
+    <row r="17" ht="10" customHeight="1"/>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="9" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="10" t="inlineStr"/>
+      <c r="K19" s="11" t="inlineStr">
+        <is>
+          <t>현장대리인</t>
+        </is>
+      </c>
+      <c r="Q19" s="12" t="inlineStr">
+        <is>
+          <t>김철수</t>
+        </is>
+      </c>
+      <c r="U19" s="13" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="6" customHeight="1"/>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>────────────  검 측 결 과 통 보  ────────────</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="6" customHeight="1"/>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  번        호</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>검측결과 제2026-041호</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="5" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
+      <c r="Q23" s="5" t="n"/>
+      <c r="R23" s="5" t="n"/>
+      <c r="S23" s="5" t="n"/>
+      <c r="T23" s="5" t="n"/>
+      <c r="U23" s="5" t="n"/>
+      <c r="V23" s="5" t="n"/>
+      <c r="W23" s="5" t="n"/>
+      <c r="X23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  수        신</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>현장대리인 귀하</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="5" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
+      <c r="M24" s="5" t="n"/>
+      <c r="N24" s="5" t="n"/>
+      <c r="O24" s="5" t="n"/>
+      <c r="P24" s="5" t="n"/>
+      <c r="Q24" s="5" t="n"/>
+      <c r="R24" s="5" t="n"/>
+      <c r="S24" s="5" t="n"/>
+      <c r="T24" s="5" t="n"/>
+      <c r="U24" s="5" t="n"/>
+      <c r="V24" s="5" t="n"/>
+      <c r="W24" s="5" t="n"/>
+      <c r="X24" s="5" t="n"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  검 측 일 시</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>2026. 9. 29. 10:20</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="5" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
+      <c r="M25" s="5" t="n"/>
+      <c r="N25" s="5" t="n"/>
+      <c r="O25" s="5" t="n"/>
+      <c r="P25" s="5" t="n"/>
+      <c r="Q25" s="5" t="n"/>
+      <c r="R25" s="5" t="n"/>
+      <c r="S25" s="5" t="n"/>
+      <c r="T25" s="5" t="n"/>
+      <c r="U25" s="5" t="n"/>
+      <c r="V25" s="5" t="n"/>
+      <c r="W25" s="5" t="n"/>
+      <c r="X25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  검 측 결 과</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>☑ 합격          ☐ 불합격 (조치 후 재검측)</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
+      <c r="M26" s="5" t="n"/>
+      <c r="N26" s="5" t="n"/>
+      <c r="O26" s="5" t="n"/>
+      <c r="P26" s="5" t="n"/>
+      <c r="Q26" s="5" t="n"/>
+      <c r="R26" s="5" t="n"/>
+      <c r="S26" s="5" t="n"/>
+      <c r="T26" s="5" t="n"/>
+      <c r="U26" s="5" t="n"/>
+      <c r="V26" s="5" t="n"/>
+      <c r="W26" s="5" t="n"/>
+      <c r="X26" s="5" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  지 적 사 항</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>없음 — 되메우기 진행 가능</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
+      <c r="N27" s="5" t="n"/>
+      <c r="O27" s="5" t="n"/>
+      <c r="P27" s="5" t="n"/>
+      <c r="Q27" s="5" t="n"/>
+      <c r="R27" s="5" t="n"/>
+      <c r="S27" s="5" t="n"/>
+      <c r="T27" s="5" t="n"/>
+      <c r="U27" s="5" t="n"/>
+      <c r="V27" s="5" t="n"/>
+      <c r="W27" s="5" t="n"/>
+      <c r="X27" s="5" t="n"/>
+    </row>
+    <row r="28" ht="6" customHeight="1"/>
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>위 검측요청서 번호에 대한 검측결과를 다음과 같이 통보합니다.  붙임 : 감리원의 검측 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="6" customHeight="1"/>
+    <row r="31" ht="10" customHeight="1"/>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="9" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="10" t="inlineStr"/>
+      <c r="K33" s="11" t="inlineStr">
+        <is>
+          <t>검측 감리원</t>
+        </is>
+      </c>
+      <c r="Q33" s="12" t="inlineStr">
+        <is>
+          <t>박감리</t>
+        </is>
+      </c>
+      <c r="U33" s="13" t="inlineStr">
+        <is>
+          <t>(서명 또는 인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="6" customHeight="1"/>
+    <row r="36" ht="19.5" customHeight="1">
+      <c r="A36" s="14" t="inlineStr">
+        <is>
+          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="42">
+    <mergeCell ref="U33:X33"/>
+    <mergeCell ref="G7:X7"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="G10:X10"/>
+    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="G6:X6"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A18:X18"/>
+    <mergeCell ref="A3:X3"/>
+    <mergeCell ref="U19:X19"/>
+    <mergeCell ref="A21:X21"/>
+    <mergeCell ref="G24:X24"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="G5:X5"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A32:X32"/>
+    <mergeCell ref="G26:X26"/>
+    <mergeCell ref="Q33:T33"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A29:X29"/>
+    <mergeCell ref="K19:P19"/>
+    <mergeCell ref="G25:X25"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="G9:X9"/>
+    <mergeCell ref="A13:X13"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="Q19:T19"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="K33:P33"/>
+    <mergeCell ref="G11:X11"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A15:X15"/>
+    <mergeCell ref="G27:X27"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="M1:X1"/>
+    <mergeCell ref="A36:X36"/>
+    <mergeCell ref="G23:X23"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G8:X8"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/web/public/forms/geomcheuk-yocheong.xlsx
+++ b/web/public/forms/geomcheuk-yocheong.xlsx
@@ -558,7 +558,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="M1" s="15" t="inlineStr">

--- a/web/public/forms/geomcheuk-yocheong.xlsx
+++ b/web/public/forms/geomcheuk-yocheong.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="검측요청서 · 검측결과통보" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'검측요청서 · 검측결과통보'!$A$1:$X$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$X$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -116,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -157,9 +155,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1028,6 +1023,7 @@
       </c>
     </row>
     <row r="34" ht="6" customHeight="1"/>
+    <row r="35"/>
     <row r="36" ht="34" customHeight="1">
       <c r="A36" s="14" t="inlineStr">
         <is>
@@ -1092,609 +1088,4 @@
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:X36"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3.6" customWidth="1" min="1" max="1"/>
-    <col width="3.6" customWidth="1" min="2" max="2"/>
-    <col width="3.6" customWidth="1" min="3" max="3"/>
-    <col width="3.6" customWidth="1" min="4" max="4"/>
-    <col width="3.6" customWidth="1" min="5" max="5"/>
-    <col width="3.6" customWidth="1" min="6" max="6"/>
-    <col width="3.6" customWidth="1" min="7" max="7"/>
-    <col width="3.6" customWidth="1" min="8" max="8"/>
-    <col width="3.6" customWidth="1" min="9" max="9"/>
-    <col width="3.6" customWidth="1" min="10" max="10"/>
-    <col width="3.6" customWidth="1" min="11" max="11"/>
-    <col width="3.6" customWidth="1" min="12" max="12"/>
-    <col width="3.6" customWidth="1" min="13" max="13"/>
-    <col width="3.6" customWidth="1" min="14" max="14"/>
-    <col width="3.6" customWidth="1" min="15" max="15"/>
-    <col width="3.6" customWidth="1" min="16" max="16"/>
-    <col width="3.6" customWidth="1" min="17" max="17"/>
-    <col width="3.6" customWidth="1" min="18" max="18"/>
-    <col width="3.6" customWidth="1" min="19" max="19"/>
-    <col width="3.6" customWidth="1" min="20" max="20"/>
-    <col width="3.6" customWidth="1" min="21" max="21"/>
-    <col width="3.6" customWidth="1" min="22" max="22"/>
-    <col width="3.6" customWidth="1" min="23" max="23"/>
-    <col width="3.6" customWidth="1" min="24" max="24"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="M1" s="15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="6" customHeight="1"/>
-    <row r="3" ht="38" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>검 측 요 청 서</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="10" customHeight="1"/>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  번        호</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>검측 제2026-041호</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="5" t="n"/>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
-      <c r="M5" s="5" t="n"/>
-      <c r="N5" s="5" t="n"/>
-      <c r="O5" s="5" t="n"/>
-      <c r="P5" s="5" t="n"/>
-      <c r="Q5" s="5" t="n"/>
-      <c r="R5" s="5" t="n"/>
-      <c r="S5" s="5" t="n"/>
-      <c r="T5" s="5" t="n"/>
-      <c r="U5" s="5" t="n"/>
-      <c r="V5" s="5" t="n"/>
-      <c r="W5" s="5" t="n"/>
-      <c r="X5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  요 청 일 자</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="7" t="n">
-        <v>46293</v>
-      </c>
-      <c r="H6" s="5" t="n"/>
-      <c r="I6" s="5" t="n"/>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-      <c r="M6" s="5" t="n"/>
-      <c r="N6" s="5" t="n"/>
-      <c r="O6" s="5" t="n"/>
-      <c r="P6" s="5" t="n"/>
-      <c r="Q6" s="5" t="n"/>
-      <c r="R6" s="5" t="n"/>
-      <c r="S6" s="5" t="n"/>
-      <c r="T6" s="5" t="n"/>
-      <c r="U6" s="5" t="n"/>
-      <c r="V6" s="5" t="n"/>
-      <c r="W6" s="5" t="n"/>
-      <c r="X6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  수        신</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>책임감리원 귀하</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-      <c r="M7" s="5" t="n"/>
-      <c r="N7" s="5" t="n"/>
-      <c r="O7" s="5" t="n"/>
-      <c r="P7" s="5" t="n"/>
-      <c r="Q7" s="5" t="n"/>
-      <c r="R7" s="5" t="n"/>
-      <c r="S7" s="5" t="n"/>
-      <c r="T7" s="5" t="n"/>
-      <c r="U7" s="5" t="n"/>
-      <c r="V7" s="5" t="n"/>
-      <c r="W7" s="5" t="n"/>
-      <c r="X7" s="5" t="n"/>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  위치 및 공종</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="6" t="inlineStr">
-        <is>
-          <t>STA.0+420 ~ 0+462 · 배수공(PE관 D600)</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n"/>
-      <c r="I8" s="5" t="n"/>
-      <c r="J8" s="5" t="n"/>
-      <c r="K8" s="5" t="n"/>
-      <c r="L8" s="5" t="n"/>
-      <c r="M8" s="5" t="n"/>
-      <c r="N8" s="5" t="n"/>
-      <c r="O8" s="5" t="n"/>
-      <c r="P8" s="5" t="n"/>
-      <c r="Q8" s="5" t="n"/>
-      <c r="R8" s="5" t="n"/>
-      <c r="S8" s="5" t="n"/>
-      <c r="T8" s="5" t="n"/>
-      <c r="U8" s="5" t="n"/>
-      <c r="V8" s="5" t="n"/>
-      <c r="W8" s="5" t="n"/>
-      <c r="X8" s="5" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  검 측 부 위</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>관 기초·부설·접합부</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="5" t="n"/>
-      <c r="J9" s="5" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
-      <c r="M9" s="5" t="n"/>
-      <c r="N9" s="5" t="n"/>
-      <c r="O9" s="5" t="n"/>
-      <c r="P9" s="5" t="n"/>
-      <c r="Q9" s="5" t="n"/>
-      <c r="R9" s="5" t="n"/>
-      <c r="S9" s="5" t="n"/>
-      <c r="T9" s="5" t="n"/>
-      <c r="U9" s="5" t="n"/>
-      <c r="V9" s="5" t="n"/>
-      <c r="W9" s="5" t="n"/>
-      <c r="X9" s="5" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  검측 요구일시</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>2026. 9. 29. 10:00</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="n"/>
-      <c r="I10" s="5" t="n"/>
-      <c r="J10" s="5" t="n"/>
-      <c r="K10" s="5" t="n"/>
-      <c r="L10" s="5" t="n"/>
-      <c r="M10" s="5" t="n"/>
-      <c r="N10" s="5" t="n"/>
-      <c r="O10" s="5" t="n"/>
-      <c r="P10" s="5" t="n"/>
-      <c r="Q10" s="5" t="n"/>
-      <c r="R10" s="5" t="n"/>
-      <c r="S10" s="5" t="n"/>
-      <c r="T10" s="5" t="n"/>
-      <c r="U10" s="5" t="n"/>
-      <c r="V10" s="5" t="n"/>
-      <c r="W10" s="5" t="n"/>
-      <c r="X10" s="5" t="n"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  검 측 사 항</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>관 기초 모래 두께 · 관 구배 · 접합 수밀</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="5" t="n"/>
-      <c r="J11" s="5" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="5" t="n"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
-      <c r="P11" s="5" t="n"/>
-      <c r="Q11" s="5" t="n"/>
-      <c r="R11" s="5" t="n"/>
-      <c r="S11" s="5" t="n"/>
-      <c r="T11" s="5" t="n"/>
-      <c r="U11" s="5" t="n"/>
-      <c r="V11" s="5" t="n"/>
-      <c r="W11" s="5" t="n"/>
-      <c r="X11" s="5" t="n"/>
-    </row>
-    <row r="12" ht="6" customHeight="1"/>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>위와 같이 세부공종에 대하여 검측을 요청하오니 검사 후 승인하여 주시기 바랍니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="6" customHeight="1"/>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>첨부 : 시공점검표(체크리스트) 점검결과 · 시험성과 · 야장 및 도면 · 공사참여자(기능공 포함) 명단 · 측량결과</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="6" customHeight="1"/>
-    <row r="17" ht="10" customHeight="1"/>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="9" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="10" t="inlineStr"/>
-      <c r="K19" s="11" t="inlineStr">
-        <is>
-          <t>현장대리인</t>
-        </is>
-      </c>
-      <c r="Q19" s="12" t="inlineStr">
-        <is>
-          <t>김철수</t>
-        </is>
-      </c>
-      <c r="U19" s="13" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="6" customHeight="1"/>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>────────────  검 측 결 과 통 보  ────────────</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="6" customHeight="1"/>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  번        호</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>검측결과 제2026-041호</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="n"/>
-      <c r="I23" s="5" t="n"/>
-      <c r="J23" s="5" t="n"/>
-      <c r="K23" s="5" t="n"/>
-      <c r="L23" s="5" t="n"/>
-      <c r="M23" s="5" t="n"/>
-      <c r="N23" s="5" t="n"/>
-      <c r="O23" s="5" t="n"/>
-      <c r="P23" s="5" t="n"/>
-      <c r="Q23" s="5" t="n"/>
-      <c r="R23" s="5" t="n"/>
-      <c r="S23" s="5" t="n"/>
-      <c r="T23" s="5" t="n"/>
-      <c r="U23" s="5" t="n"/>
-      <c r="V23" s="5" t="n"/>
-      <c r="W23" s="5" t="n"/>
-      <c r="X23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  수        신</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>현장대리인 귀하</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
-      <c r="K24" s="5" t="n"/>
-      <c r="L24" s="5" t="n"/>
-      <c r="M24" s="5" t="n"/>
-      <c r="N24" s="5" t="n"/>
-      <c r="O24" s="5" t="n"/>
-      <c r="P24" s="5" t="n"/>
-      <c r="Q24" s="5" t="n"/>
-      <c r="R24" s="5" t="n"/>
-      <c r="S24" s="5" t="n"/>
-      <c r="T24" s="5" t="n"/>
-      <c r="U24" s="5" t="n"/>
-      <c r="V24" s="5" t="n"/>
-      <c r="W24" s="5" t="n"/>
-      <c r="X24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  검 측 일 시</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>2026. 9. 29. 10:20</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="n"/>
-      <c r="I25" s="5" t="n"/>
-      <c r="J25" s="5" t="n"/>
-      <c r="K25" s="5" t="n"/>
-      <c r="L25" s="5" t="n"/>
-      <c r="M25" s="5" t="n"/>
-      <c r="N25" s="5" t="n"/>
-      <c r="O25" s="5" t="n"/>
-      <c r="P25" s="5" t="n"/>
-      <c r="Q25" s="5" t="n"/>
-      <c r="R25" s="5" t="n"/>
-      <c r="S25" s="5" t="n"/>
-      <c r="T25" s="5" t="n"/>
-      <c r="U25" s="5" t="n"/>
-      <c r="V25" s="5" t="n"/>
-      <c r="W25" s="5" t="n"/>
-      <c r="X25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="24" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  검 측 결 과</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>☑ 합격          ☐ 불합격 (조치 후 재검측)</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-      <c r="N26" s="5" t="n"/>
-      <c r="O26" s="5" t="n"/>
-      <c r="P26" s="5" t="n"/>
-      <c r="Q26" s="5" t="n"/>
-      <c r="R26" s="5" t="n"/>
-      <c r="S26" s="5" t="n"/>
-      <c r="T26" s="5" t="n"/>
-      <c r="U26" s="5" t="n"/>
-      <c r="V26" s="5" t="n"/>
-      <c r="W26" s="5" t="n"/>
-      <c r="X26" s="5" t="n"/>
-    </row>
-    <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  지 적 사 항</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n"/>
-      <c r="C27" s="5" t="n"/>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>없음 — 되메우기 진행 가능</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="n"/>
-      <c r="I27" s="5" t="n"/>
-      <c r="J27" s="5" t="n"/>
-      <c r="K27" s="5" t="n"/>
-      <c r="L27" s="5" t="n"/>
-      <c r="M27" s="5" t="n"/>
-      <c r="N27" s="5" t="n"/>
-      <c r="O27" s="5" t="n"/>
-      <c r="P27" s="5" t="n"/>
-      <c r="Q27" s="5" t="n"/>
-      <c r="R27" s="5" t="n"/>
-      <c r="S27" s="5" t="n"/>
-      <c r="T27" s="5" t="n"/>
-      <c r="U27" s="5" t="n"/>
-      <c r="V27" s="5" t="n"/>
-      <c r="W27" s="5" t="n"/>
-      <c r="X27" s="5" t="n"/>
-    </row>
-    <row r="28" ht="6" customHeight="1"/>
-    <row r="29" ht="34" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>위 검측요청서 번호에 대한 검측결과를 다음과 같이 통보합니다.  붙임 : 감리원의 검측 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="6" customHeight="1"/>
-    <row r="31" ht="10" customHeight="1"/>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="9" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="33" ht="24" customHeight="1">
-      <c r="A33" s="10" t="inlineStr"/>
-      <c r="K33" s="11" t="inlineStr">
-        <is>
-          <t>검측 감리원</t>
-        </is>
-      </c>
-      <c r="Q33" s="12" t="inlineStr">
-        <is>
-          <t>박감리</t>
-        </is>
-      </c>
-      <c r="U33" s="13" t="inlineStr">
-        <is>
-          <t>(서명 또는 인)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="6" customHeight="1"/>
-    <row r="36" ht="19.5" customHeight="1">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 현장 · 이름 · 금액). 실제로는 앞 시트에 적으세요.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="42">
-    <mergeCell ref="U33:X33"/>
-    <mergeCell ref="G7:X7"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="G10:X10"/>
-    <mergeCell ref="A33:J33"/>
-    <mergeCell ref="G6:X6"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A18:X18"/>
-    <mergeCell ref="A3:X3"/>
-    <mergeCell ref="U19:X19"/>
-    <mergeCell ref="A21:X21"/>
-    <mergeCell ref="G24:X24"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="G5:X5"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A32:X32"/>
-    <mergeCell ref="G26:X26"/>
-    <mergeCell ref="Q33:T33"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A29:X29"/>
-    <mergeCell ref="K19:P19"/>
-    <mergeCell ref="G25:X25"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="G9:X9"/>
-    <mergeCell ref="A13:X13"/>
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="Q19:T19"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="K33:P33"/>
-    <mergeCell ref="G11:X11"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A15:X15"/>
-    <mergeCell ref="G27:X27"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="M1:X1"/>
-    <mergeCell ref="A36:X36"/>
-    <mergeCell ref="G23:X23"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G8:X8"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/web/public/forms/geomcheuk-yocheong.xlsx
+++ b/web/public/forms/geomcheuk-yocheong.xlsx
@@ -553,7 +553,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
